--- a/knowledge/users.xlsx
+++ b/knowledge/users.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -487,9 +487,41 @@
         <v>MB123</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Mrs. Lena</v>
+      </c>
+      <c r="B12" t="str">
+        <v>L.is.ai.developer</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Mrs. Nora</v>
+      </c>
+      <c r="B13" t="str">
+        <v>N123</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Mrs. Barig</v>
+      </c>
+      <c r="B14" t="str">
+        <v>B.is.awesome</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Mrs. Lara</v>
+      </c>
+      <c r="B15" t="str">
+        <v>L.takes.no.breaks</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/knowledge/users.xlsx
+++ b/knowledge/users.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:C16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -406,6 +406,9 @@
       <c r="B1" t="str">
         <v>code</v>
       </c>
+      <c r="C1" t="str">
+        <v>mode</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -414,6 +417,9 @@
       <c r="B2" t="str">
         <v>YB123</v>
       </c>
+      <c r="C2" t="str">
+        <v>admin</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -422,6 +428,9 @@
       <c r="B3" t="str">
         <v>M.is.support.system</v>
       </c>
+      <c r="C3" t="str">
+        <v>teacher</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -519,9 +528,17 @@
         <v>L.takes.no.breaks</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Vartan</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Vartan.is.gay</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>